--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484096_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484096_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8304</v>
+        <v>7.4156</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6266</v>
+        <v>5.791</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2038</v>
+        <v>1.6246</v>
       </c>
       <c r="G2" t="n">
         <v>7.8158</v>
@@ -610,13 +610,13 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5526</v>
+        <v>0.0326</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1926</v>
+        <v>-0.0283</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.36</v>
+        <v>0.0608</v>
       </c>
       <c r="V2" t="n">
         <v>-2.2182</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.7933</v>
+        <v>6.4475</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8499</v>
+        <v>5.5041</v>
       </c>
       <c r="F3" t="n">
         <v>0.9434</v>
@@ -688,10 +688,10 @@
         <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7312</v>
+        <v>0.3854</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6122</v>
+        <v>0.2665</v>
       </c>
       <c r="U3" t="n">
         <v>0.1189</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.7602</v>
+        <v>5.8138</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0516</v>
+        <v>4.1333</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7085</v>
+        <v>1.6805</v>
       </c>
       <c r="G4" t="n">
         <v>3.3832</v>
@@ -766,13 +766,13 @@
         <v>2.1822</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1352</v>
+        <v>1.1889</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9726</v>
+        <v>1.0544</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1626</v>
+        <v>0.1345</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9405</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.0008</v>
+        <v>4.7391</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3923</v>
+        <v>3.0465</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6085</v>
+        <v>1.6926</v>
       </c>
       <c r="G5" t="n">
         <v>5.5389</v>
@@ -844,13 +844,13 @@
         <v>1.3887</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5889</v>
+        <v>0.3273</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.2041</v>
       </c>
       <c r="U5" t="n">
-        <v>0.039</v>
+        <v>0.1232</v>
       </c>
       <c r="V5" t="n">
         <v>-0.532</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.6813</v>
+        <v>4.1711</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4852</v>
+        <v>1.9751</v>
       </c>
       <c r="F6" t="n">
         <v>2.1961</v>
@@ -922,10 +922,10 @@
         <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0883</v>
+        <v>0.5782</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9807</v>
+        <v>0.4706</v>
       </c>
       <c r="U6" t="n">
         <v>0.1076</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.6755</v>
+        <v>4.1512</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1734</v>
+        <v>2.9296</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5021</v>
+        <v>1.2216</v>
       </c>
       <c r="G7" t="n">
         <v>2.0593</v>
@@ -1000,13 +1000,13 @@
         <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9579</v>
+        <v>0.4336</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6122</v>
+        <v>0.3685</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3456</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0.0713</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8218</v>
+        <v>3.4494</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6860000000000001</v>
+        <v>1.7063</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1358</v>
+        <v>1.743</v>
       </c>
       <c r="G8" t="n">
         <v>2.0457</v>
@@ -1078,13 +1078,13 @@
         <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4773</v>
+        <v>0.1502</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1222</v>
+        <v>-0.1019</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6449</v>
+        <v>0.2521</v>
       </c>
       <c r="V8" t="n">
         <v>-0.532</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3265</v>
+        <v>2.0112</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0094</v>
+        <v>0.5819</v>
       </c>
       <c r="F9" t="n">
-        <v>1.317</v>
+        <v>1.4293</v>
       </c>
       <c r="G9" t="n">
         <v>1.8198</v>
@@ -1156,13 +1156,13 @@
         <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2515</v>
+        <v>-0.5668</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0599</v>
+        <v>-0.4874</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1917</v>
+        <v>-0.0794</v>
       </c>
       <c r="V9" t="n">
         <v>2.1469</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8224</v>
+        <v>0.9065</v>
       </c>
       <c r="E10" t="n">
         <v>0.701</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1213</v>
+        <v>0.2055</v>
       </c>
       <c r="G10" t="n">
         <v>0.8339</v>
@@ -1234,13 +1234,13 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1423</v>
+        <v>-0.0581</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0623</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0799</v>
+        <v>0.0042</v>
       </c>
       <c r="V10" t="n">
         <v>-0.266</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6023</v>
+        <v>-1.1661</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.2114</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9827</v>
+        <v>-0.9547</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2684</v>
@@ -1312,13 +1312,13 @@
         <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.242</v>
+        <v>0.1941</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.442</v>
+        <v>-0.0339</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.228</v>
       </c>
       <c r="V11" t="n">
         <v>-2.6789</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4208</v>
+        <v>-3.9387</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8731</v>
+        <v>-3.3629</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5477</v>
+        <v>-0.5758</v>
       </c>
       <c r="G12" t="n">
         <v>-1.813</v>
@@ -1390,13 +1390,13 @@
         <v>1.3887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5402</v>
+        <v>-0.0581</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3173</v>
+        <v>0.1928</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2228</v>
+        <v>-0.2509</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4724</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>33.6891</v>
+        <v>34.0006</v>
       </c>
       <c r="E13" t="n">
-        <v>22.4828</v>
+        <v>22.7945</v>
       </c>
       <c r="F13" t="n">
         <v>11.2061</v>
@@ -1468,13 +1468,13 @@
         <v>15.871</v>
       </c>
       <c r="S13" t="n">
-        <v>2.295599999999999</v>
+        <v>2.6073</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5313</v>
+        <v>1.8431</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7642000000000001</v>
+        <v>0.7641000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-2.270499999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4993</v>
+        <v>2.155</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1915</v>
+        <v>2.9875</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6922</v>
+        <v>-0.8325</v>
       </c>
       <c r="G14" t="n">
         <v>2.3176</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3089</v>
+        <v>-0.0355</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2438</v>
+        <v>0.0397</v>
       </c>
       <c r="U14" t="n">
-        <v>0.06510000000000001</v>
+        <v>-0.0752</v>
       </c>
       <c r="V14" t="n">
         <v>0.0713</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5943</v>
+        <v>1.4829</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3563</v>
+        <v>2.2543</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.762</v>
+        <v>-0.7713</v>
       </c>
       <c r="G15" t="n">
         <v>1.8815</v>
@@ -1624,13 +1624,13 @@
         <v>0.5952</v>
       </c>
       <c r="S15" t="n">
-        <v>0.161</v>
+        <v>0.0496</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0566</v>
+        <v>-0.1586</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2176</v>
+        <v>0.2082</v>
       </c>
       <c r="V15" t="n">
         <v>0.9405</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2816</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4259</v>
+        <v>-0.3238</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7074</v>
+        <v>0.8758</v>
       </c>
       <c r="G16" t="n">
         <v>0.0106</v>
@@ -1702,13 +1702,13 @@
         <v>0.3968</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1258</v>
+        <v>0.1446</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4137</v>
+        <v>-0.3117</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2879</v>
+        <v>0.4562</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2976</v>
+        <v>-1.1164</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2793</v>
+        <v>0.7691</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5769</v>
+        <v>-1.8855</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8627</v>
@@ -1780,13 +1780,13 @@
         <v>0.3968</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1603</v>
+        <v>0.3415</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5613</v>
+        <v>0.0511</v>
       </c>
       <c r="U17" t="n">
-        <v>0.599</v>
+        <v>0.2904</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7061</v>
+        <v>-1.7163</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4464</v>
+        <v>1.5484</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.1525</v>
+        <v>-3.2647</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6947</v>
@@ -1858,13 +1858,13 @@
         <v>0.3968</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.619</v>
+        <v>-0.6292</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0452</v>
+        <v>0.0568</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5737</v>
+        <v>-0.6859</v>
       </c>
       <c r="V18" t="n">
         <v>1.4012</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.151</v>
+        <v>-2.3832</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9414</v>
+        <v>-1.1454</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2097</v>
+        <v>-1.2377</v>
       </c>
       <c r="G19" t="n">
         <v>-2.953</v>
@@ -1936,13 +1936,13 @@
         <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4008</v>
+        <v>0.1686</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1645</v>
+        <v>-0.0396</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2363</v>
+        <v>0.2082</v>
       </c>
       <c r="V19" t="n">
         <v>0.7979000000000001</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0802</v>
+        <v>-3.098</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6879</v>
+        <v>-2.7899</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3923</v>
+        <v>-0.3082</v>
       </c>
       <c r="G20" t="n">
         <v>-2.748</v>
@@ -2014,13 +2014,13 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2035</v>
+        <v>0.1856</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1076</v>
+        <v>-0.2096</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3111</v>
+        <v>0.3953</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3373</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7494</v>
+        <v>-4.173</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8407</v>
+        <v>-2.4326</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9087</v>
+        <v>-1.7404</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3256</v>
@@ -2092,13 +2092,13 @@
         <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4239</v>
+        <v>-0.8474</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4137</v>
+        <v>-0.0056</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0101</v>
+        <v>-0.8418</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2065</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.5635</v>
+        <v>-6.9437</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7145</v>
+        <v>-0.8983</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.849</v>
+        <v>-6.0454</v>
       </c>
       <c r="G22" t="n">
         <v>-5.9362</v>
@@ -2170,13 +2170,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.429</v>
+        <v>-0.8091</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9748</v>
+        <v>-0.1586</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4541</v>
+        <v>-0.6505</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.1358</v>
+        <v>-8.2531</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0646</v>
+        <v>-5.5747</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0712</v>
+        <v>-2.6784</v>
       </c>
       <c r="G23" t="n">
         <v>-6.0749</v>
@@ -2248,13 +2248,13 @@
         <v>0.5952</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2279</v>
+        <v>0.1106</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5103</v>
+        <v>0.0001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2823</v>
+        <v>0.1105</v>
       </c>
       <c r="V23" t="n">
         <v>2.0757</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.3336</v>
+        <v>-10.2877</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.6984</v>
+        <v>-5.5963</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.6353</v>
+        <v>-4.6914</v>
       </c>
       <c r="G24" t="n">
         <v>-6.6529</v>
@@ -2326,13 +2326,13 @@
         <v>0.5952</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8196</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2436</v>
+        <v>-0.1416</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.576</v>
+        <v>-0.6321</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4724</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-33.642</v>
+        <v>-33.7816</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.0999</v>
+        <v>-11.2017</v>
       </c>
       <c r="F25" t="n">
-        <v>-22.5424</v>
+        <v>-22.5797</v>
       </c>
       <c r="G25" t="n">
         <v>-24.0383</v>
@@ -2404,13 +2404,13 @@
         <v>5.7534</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.9549</v>
+        <v>-2.0944</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7753000000000001</v>
+        <v>-0.8775999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1792</v>
+        <v>-1.2167</v>
       </c>
       <c r="V25" t="n">
         <v>2.2704</v>
